--- a/backend/data/uploads/MES/2026-07-10_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-10_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C159434-91DD-45C9-9132-79CDA02C84C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E27FCC24-2F51-4826-BDD4-363DDB3BD90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{2E0F9A71-A409-4EA9-857D-1DA51C1FB813}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{84777DED-B112-4ABD-8607-93E938A55255}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D1F45A8-B68D-48DF-8A11-D7B84CBBCC67}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF11C291-84A1-47FA-9CDE-6695AF634053}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-10_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-10_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E27FCC24-2F51-4826-BDD4-363DDB3BD90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A45129B-BE40-4A04-A9B8-21CBB2096F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{84777DED-B112-4ABD-8607-93E938A55255}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{5239E92F-1210-4574-A15B-EA485C8F56A3}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF11C291-84A1-47FA-9CDE-6695AF634053}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D46F7378-6594-4740-B787-9032DC504BE4}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-10_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-10_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A45129B-BE40-4A04-A9B8-21CBB2096F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE1E1FD9-56AB-46A6-BF8A-D379FE145317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{5239E92F-1210-4574-A15B-EA485C8F56A3}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{D65A0C46-381E-43B2-A6F8-535D039909BD}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D46F7378-6594-4740-B787-9032DC504BE4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A2F1434-3DAD-473F-9D8B-327D5F73A6A5}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
